--- a/inv/women_bags.xlsx
+++ b/inv/women_bags.xlsx
@@ -16,10 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Title</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>titleid</t>
   </si>
@@ -28,6 +25,21 @@
   </si>
   <si>
     <t>women_hand_bags</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>scat</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>?page=women_hand_bags</t>
   </si>
 </sst>
 </file>
@@ -359,23 +371,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
